--- a/parsers/data/raw/cbr/sors_02_01_Funds_all.xlsx
+++ b/parsers/data/raw/cbr/sors_02_01_Funds_all.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RukhlinaEY\AppData\Local\Temp\Rar$DIa23664.23869.rartemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RukhlinaEY\AppData\Local\Temp\Rar$DIa61496.10778.rartemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11535" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15765" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="в рублях" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="184">
   <si>
     <t>01.02.2012</t>
   </si>
@@ -534,6 +534,9 @@
   </si>
   <si>
     <t>01.04.2026</t>
+  </si>
+  <si>
+    <t>01.05.2026</t>
   </si>
   <si>
     <t>Средства клиентов, всего</t>
@@ -590,27 +593,37 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="20"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -957,16 +970,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FP10"/>
+  <dimension ref="A1:FQ10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.7109375" customWidth="1"/>
-    <col min="2" max="172" width="14.28515625" customWidth="1"/>
+    <col min="2" max="173" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:172" s="1" customFormat="1" ht="49.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:173" s="1" customFormat="1" ht="49.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -987,7 +1000,7 @@
       <c r="R1" s="6"/>
       <c r="S1" s="6"/>
     </row>
-    <row r="2" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1501,10 +1514,13 @@
       <c r="FP2" s="2" t="s">
         <v>170</v>
       </c>
+      <c r="FQ2" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="4">
         <v>19729596</v>
@@ -2019,10 +2035,13 @@
       <c r="FP3" s="4">
         <v>133976142</v>
       </c>
+      <c r="FQ3" s="4">
+        <v>135653627</v>
+      </c>
     </row>
-    <row r="4" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" s="4">
         <v>4584222</v>
@@ -2537,10 +2556,13 @@
       <c r="FP4" s="4">
         <v>20626485</v>
       </c>
+      <c r="FQ4" s="4">
+        <v>20495851</v>
+      </c>
     </row>
-    <row r="5" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" s="4">
         <v>4595879</v>
@@ -3055,10 +3077,13 @@
       <c r="FP5" s="4">
         <v>34224618</v>
       </c>
+      <c r="FQ5" s="4">
+        <v>34613343</v>
+      </c>
     </row>
-    <row r="6" spans="1:172" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:173" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" s="4">
         <v>9528877</v>
@@ -3573,262 +3598,265 @@
       <c r="FP6" s="4">
         <v>69649041</v>
       </c>
+      <c r="FQ6" s="4">
+        <v>70831794</v>
+      </c>
     </row>
-    <row r="7" spans="1:172" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:173" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AR7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AS7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AT7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AU7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AV7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AW7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AX7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AY7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BH7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BI7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BK7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BL7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BN7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BO7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BP7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BQ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BR7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BS7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BT7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BU7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BV7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BW7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BX7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BY7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BZ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CH7" s="4">
         <v>21758138</v>
@@ -4091,262 +4119,265 @@
       <c r="FP7" s="4">
         <v>62472025</v>
       </c>
+      <c r="FQ7" s="4">
+        <v>63650986</v>
+      </c>
     </row>
-    <row r="8" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AR8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AS8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AT8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AU8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AV8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AW8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AX8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AY8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BH8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BI8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BK8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BL8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BN8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BO8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BP8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BQ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BR8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BS8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BT8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BU8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BV8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BW8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BX8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BY8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BZ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CH8" s="4">
         <v>2968</v>
@@ -4609,46 +4640,49 @@
       <c r="FP8" s="4">
         <v>7176989</v>
       </c>
+      <c r="FQ8" s="4">
+        <v>7180778</v>
+      </c>
     </row>
-    <row r="9" spans="1:172" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:173" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N9" s="4">
         <v>162579</v>
@@ -5127,10 +5161,13 @@
       <c r="FP9" s="4">
         <v>2665471</v>
       </c>
+      <c r="FQ9" s="4">
+        <v>2558623</v>
+      </c>
     </row>
-    <row r="10" spans="1:172" s="1" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:173" s="1" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -5145,16 +5182,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FP10"/>
+  <dimension ref="A1:FQ10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48.140625" customWidth="1"/>
-    <col min="2" max="172" width="13.28515625" customWidth="1"/>
+    <col min="2" max="173" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:172" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:173" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -5175,7 +5212,7 @@
       <c r="R1" s="6"/>
       <c r="S1" s="6"/>
     </row>
-    <row r="2" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -5689,10 +5726,13 @@
       <c r="FP2" s="2" t="s">
         <v>170</v>
       </c>
+      <c r="FQ2" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="4">
         <v>6135568</v>
@@ -6207,10 +6247,13 @@
       <c r="FP3" s="4">
         <v>14258890</v>
       </c>
+      <c r="FQ3" s="4">
+        <v>13234529</v>
+      </c>
     </row>
-    <row r="4" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" s="4">
         <v>787260</v>
@@ -6725,10 +6768,13 @@
       <c r="FP4" s="4">
         <v>1873400</v>
       </c>
+      <c r="FQ4" s="4">
+        <v>1825013</v>
+      </c>
     </row>
-    <row r="5" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" s="4">
         <v>1723058</v>
@@ -7243,10 +7289,13 @@
       <c r="FP5" s="4">
         <v>8437439</v>
       </c>
+      <c r="FQ5" s="4">
+        <v>7723915</v>
+      </c>
     </row>
-    <row r="6" spans="1:172" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:173" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" s="4">
         <v>2101762</v>
@@ -7761,262 +7810,265 @@
       <c r="FP6" s="4">
         <v>3265653</v>
       </c>
+      <c r="FQ6" s="4">
+        <v>3043054</v>
+      </c>
     </row>
-    <row r="7" spans="1:172" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:173" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AR7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AS7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AT7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AU7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AV7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AW7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AX7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AY7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BH7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BI7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BK7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BL7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BN7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BO7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BP7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BQ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BR7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BS7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BT7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BU7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BV7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BW7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BX7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BY7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BZ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CH7" s="4">
         <v>6096876</v>
@@ -8279,262 +8331,265 @@
       <c r="FP7" s="4">
         <v>3265628</v>
       </c>
+      <c r="FQ7" s="4">
+        <v>3043031</v>
+      </c>
     </row>
-    <row r="8" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AR8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AS8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AT8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AU8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AV8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AW8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AX8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AY8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BH8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BI8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BK8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BL8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BN8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BO8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BP8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BQ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BR8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BS8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BT8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BU8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BV8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BW8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BX8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BY8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BZ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CH8" s="4">
         <v>0</v>
@@ -8797,46 +8852,49 @@
       <c r="FP8" s="4">
         <v>0</v>
       </c>
+      <c r="FQ8" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:172" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:173" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N9" s="4">
         <v>2582</v>
@@ -9315,10 +9373,13 @@
       <c r="FP9" s="4">
         <v>27153</v>
       </c>
+      <c r="FQ9" s="4">
+        <v>26528</v>
+      </c>
     </row>
-    <row r="10" spans="1:172" s="1" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:173" s="1" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -9333,16 +9394,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FP10"/>
+  <dimension ref="A1:FQ10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
-    <col min="2" max="172" width="14.28515625" customWidth="1"/>
+    <col min="2" max="173" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:172" s="1" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:173" s="1" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -9363,7 +9424,7 @@
       <c r="R1" s="7"/>
       <c r="S1" s="7"/>
     </row>
-    <row r="2" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -9877,10 +9938,13 @@
       <c r="FP2" s="2" t="s">
         <v>170</v>
       </c>
+      <c r="FQ2" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="4">
         <v>25865164</v>
@@ -10395,10 +10459,13 @@
       <c r="FP3" s="4">
         <v>148235032</v>
       </c>
+      <c r="FQ3" s="4">
+        <v>148888156</v>
+      </c>
     </row>
-    <row r="4" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" s="4">
         <v>5371482</v>
@@ -10913,10 +10980,13 @@
       <c r="FP4" s="4">
         <v>22499886</v>
       </c>
+      <c r="FQ4" s="4">
+        <v>22320864</v>
+      </c>
     </row>
-    <row r="5" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" s="4">
         <v>6318938</v>
@@ -11431,10 +11501,13 @@
       <c r="FP5" s="4">
         <v>42662057</v>
       </c>
+      <c r="FQ5" s="4">
+        <v>42337258</v>
+      </c>
     </row>
-    <row r="6" spans="1:172" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:173" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" s="4">
         <v>11630639</v>
@@ -11949,262 +12022,265 @@
       <c r="FP6" s="4">
         <v>72914694</v>
       </c>
+      <c r="FQ6" s="4">
+        <v>73874848</v>
+      </c>
     </row>
-    <row r="7" spans="1:172" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:173" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AR7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AS7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AT7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AU7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AV7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AW7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AX7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AY7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BH7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BI7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BK7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BL7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BN7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BO7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BP7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BQ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BR7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BS7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BT7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BU7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BV7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BW7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BX7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BY7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BZ7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CA7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CB7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CC7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CD7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CF7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CG7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CH7" s="4">
         <v>27855014</v>
@@ -12467,262 +12543,265 @@
       <c r="FP7" s="4">
         <v>65737653</v>
       </c>
+      <c r="FQ7" s="4">
+        <v>66694017</v>
+      </c>
     </row>
-    <row r="8" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AP8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AQ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AR8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AS8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AT8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AU8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AV8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AW8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AX8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AY8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BH8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BI8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BK8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BL8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BN8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BO8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BP8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BQ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BR8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BS8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BT8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BU8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BV8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BW8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BX8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BY8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BZ8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CA8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CB8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CC8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CD8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CF8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CG8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CH8" s="4">
         <v>2968</v>
@@ -12985,46 +13064,49 @@
       <c r="FP8" s="4">
         <v>7176989</v>
       </c>
+      <c r="FQ8" s="4">
+        <v>7180778</v>
+      </c>
     </row>
-    <row r="9" spans="1:172" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:173" s="1" customFormat="1" ht="42.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N9" s="4">
         <v>165161</v>
@@ -13503,10 +13585,13 @@
       <c r="FP9" s="4">
         <v>2692624</v>
       </c>
+      <c r="FQ9" s="4">
+        <v>2585151</v>
+      </c>
     </row>
-    <row r="10" spans="1:172" s="1" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:173" s="1" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
